--- a/E/MKTN5.xlsx
+++ b/E/MKTN5.xlsx
@@ -1702,7 +1702,7 @@
     <t>20094681</t>
   </si>
   <si>
-    <t>PMBYARAN XL HOME</t>
+    <t>PMBYARAN XL SATU</t>
   </si>
   <si>
     <t>416</t>

--- a/E/MKTN5.xlsx
+++ b/E/MKTN5.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1006">
   <si>
     <t/>
   </si>
@@ -3421,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F335"/>
+  <dimension ref="A1:H335"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3429,10 +3429,11 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3449,6 +3450,12 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4370,7 +4377,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>165</v>
       </c>
@@ -4386,7 +4393,7 @@
       <c r="E56" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/E/MKTN5.xlsx
+++ b/E/MKTN5.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1006">
   <si>
     <t/>
   </si>
@@ -3421,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H335"/>
+  <dimension ref="A1:F335"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3429,11 +3429,10 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3450,12 +3449,6 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4377,7 +4370,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>165</v>
       </c>
@@ -4393,7 +4386,7 @@
       <c r="E56" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/E/MKTN5.xlsx
+++ b/E/MKTN5.xlsx
@@ -493,7 +493,7 @@
     <t>20022280</t>
   </si>
   <si>
-    <t>PMBYRN OTO MULTIARTA</t>
+    <t>PMBYRN OTO KRDT MOBL</t>
   </si>
   <si>
     <t>167</t>
@@ -586,7 +586,7 @@
     <t>20052510</t>
   </si>
   <si>
-    <t>PMBYRN OTO SUMMT FNC</t>
+    <t>PMBYRN OTO KRDT MOTR</t>
   </si>
   <si>
     <t>185</t>
